--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484034_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484034_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0494</v>
+        <v>1.8131</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3113</v>
+        <v>-0.8486</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3608</v>
+        <v>2.6616</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1503</v>
+        <v>0.3791</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1568</v>
+        <v>-0.2519</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0065</v>
+        <v>0.631</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8615</v>
+        <v>0.353</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.2727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2461</v>
+        <v>0.0803</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0118</v>
+        <v>0.026</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7723</v>
+        <v>-0.5246</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2396</v>
+        <v>0.5507</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>2.579</v>
+        <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5208</v>
+        <v>0.4223</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8047</v>
+        <v>-0.2097</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3256</v>
+        <v>0.6319</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0757</v>
+        <v>1.0118</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6076</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.532</v>
+        <v>1.0118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0109</v>
+        <v>1.7877</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7068</v>
+        <v>1.0134</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7178</v>
+        <v>0.7743</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3791</v>
+        <v>1.3881</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2519</v>
+        <v>-0.9529</v>
       </c>
       <c r="I3" t="n">
-        <v>0.631</v>
+        <v>2.341</v>
       </c>
       <c r="J3" t="n">
-        <v>0.353</v>
+        <v>2.085</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2727</v>
+        <v>-0.3725</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0803</v>
+        <v>2.4575</v>
       </c>
       <c r="M3" t="n">
-        <v>0.026</v>
+        <v>-0.697</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5246</v>
+        <v>-0.5804</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5507</v>
+        <v>-0.1165</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6201</v>
+        <v>-0.5923</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0679</v>
+        <v>-0.3457</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6879999999999999</v>
+        <v>-0.2467</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0118</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>1.0118</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3847</v>
+        <v>1.5725</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1155</v>
+        <v>-0.3113</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2693</v>
+        <v>1.8838</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3881</v>
+        <v>-0.1503</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9529</v>
+        <v>-0.1568</v>
       </c>
       <c r="I4" t="n">
-        <v>2.341</v>
+        <v>0.0065</v>
       </c>
       <c r="J4" t="n">
-        <v>2.085</v>
+        <v>0.8615</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3725</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4575</v>
+        <v>0.2461</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.697</v>
+        <v>-1.0118</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5804</v>
+        <v>-0.7723</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1165</v>
+        <v>-0.2396</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9838</v>
+        <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9953</v>
+        <v>0.0439</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2436</v>
+        <v>-0.8047</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7516</v>
+        <v>0.8486</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>2.6076</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0979</v>
+        <v>0.2678</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2171</v>
+        <v>-0.5036</v>
       </c>
       <c r="F5" t="n">
-        <v>0.315</v>
+        <v>0.7714</v>
       </c>
       <c r="G5" t="n">
-        <v>1.541</v>
+        <v>2.9678</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3582</v>
+        <v>0.413</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8992</v>
+        <v>2.5548</v>
       </c>
       <c r="J5" t="n">
-        <v>3.123</v>
+        <v>2.8632</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7057</v>
+        <v>0.3279</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4174</v>
+        <v>2.5353</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.582</v>
+        <v>0.1046</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0639</v>
+        <v>0.0851</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5182</v>
+        <v>0.0195</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.5709</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.9596</v>
+        <v>-2.9758</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3894</v>
+        <v>-0.3033</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1189</v>
+        <v>-0.391</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5084</v>
+        <v>0.0878</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7384</v>
+        <v>-1.2065</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0878</v>
+        <v>0.1545</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4535</v>
+        <v>-0.3514</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3656</v>
+        <v>0.5059</v>
       </c>
       <c r="G6" t="n">
         <v>0.8729</v>
@@ -922,13 +922,13 @@
         <v>0.3968</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3656</v>
+        <v>-0.1233</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.187</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1786</v>
+        <v>-0.0383</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.125</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7727</v>
+        <v>-0.3588</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8977</v>
+        <v>0.287</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0617</v>
+        <v>1.541</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1511</v>
+        <v>-0.3582</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08939999999999999</v>
+        <v>1.8992</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3305</v>
+        <v>3.123</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2903</v>
+        <v>0.7057</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>2.4174</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2688</v>
+        <v>-1.582</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1392</v>
+        <v>-1.0639</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1295</v>
+        <v>-0.5182</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7935</v>
+        <v>-3.5709</v>
       </c>
       <c r="Q7" t="n">
+        <v>-4.9596</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3887</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.2607</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.7935</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2262</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.4422</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.216</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.2065</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3087</v>
+        <v>-0.1825</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9117</v>
+        <v>1.631</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6031</v>
+        <v>-1.8135</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9678</v>
+        <v>0.0617</v>
       </c>
       <c r="H8" t="n">
-        <v>0.413</v>
+        <v>0.1511</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5548</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8632</v>
+        <v>1.3305</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3279</v>
+        <v>1.2903</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5353</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1046</v>
+        <v>-1.2688</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0851</v>
+        <v>-1.1392</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0195</v>
+        <v>-0.1295</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8797</v>
+        <v>0.1686</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7991</v>
+        <v>0.3004</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0806</v>
+        <v>-0.1318</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7624</v>
+        <v>-1.4283</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8773</v>
+        <v>-2.5712</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1149</v>
+        <v>1.1429</v>
       </c>
       <c r="G9" t="n">
         <v>0.8376</v>
@@ -1156,13 +1156,13 @@
         <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3384</v>
+        <v>-0.0043</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7537</v>
+        <v>-0.4477</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4153</v>
+        <v>0.4434</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6745</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6896</v>
+        <v>-3.1782</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0464</v>
+        <v>-2.086</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6433</v>
+        <v>-1.0922</v>
       </c>
       <c r="G10" t="n">
         <v>-1.524</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8343</v>
+        <v>0.3457</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.255</v>
+        <v>-0.2947</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0893</v>
+        <v>0.6404</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4446</v>
+        <v>-6.1961</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7685</v>
+        <v>-6.6041</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3239</v>
+        <v>0.408</v>
       </c>
       <c r="G11" t="n">
         <v>-5.7096</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.442</v>
+        <v>-0.2776</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3734</v>
+        <v>0.4576</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0713</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.875200000000001</v>
+        <v>-5.461399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.4044</v>
+        <v>-10.9906</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5294</v>
+        <v>5.5292</v>
       </c>
       <c r="G12" t="n">
         <v>0.6642999999999999</v>
@@ -1369,7 +1369,7 @@
         <v>3.6067</v>
       </c>
       <c r="L12" t="n">
-        <v>4.436399999999999</v>
+        <v>4.436400000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-7.3789</v>
@@ -1378,7 +1378,7 @@
         <v>-7.5414</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1625999999999998</v>
+        <v>0.1625999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-6.9436</v>
@@ -1390,16 +1390,16 @@
         <v>14.8788</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.05679999999999974</v>
+        <v>0.3568999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.2297</v>
+        <v>-2.8164</v>
       </c>
       <c r="U12" t="n">
         <v>3.1732</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4606000000000005</v>
+        <v>0.4606000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>5.6046</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4651</v>
+        <v>4.7568</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7129</v>
+        <v>2.8966</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7522</v>
+        <v>1.8602</v>
       </c>
       <c r="G13" t="n">
         <v>3.285</v>
@@ -1468,13 +1468,13 @@
         <v>0.5952</v>
       </c>
       <c r="S13" t="n">
-        <v>1.319</v>
+        <v>0.6107</v>
       </c>
       <c r="T13" t="n">
-        <v>0.924</v>
+        <v>0.1077</v>
       </c>
       <c r="U13" t="n">
-        <v>0.395</v>
+        <v>0.503</v>
       </c>
       <c r="V13" t="n">
         <v>0.266</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7767</v>
+        <v>4.3623</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8904</v>
+        <v>1.3358</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6672</v>
+        <v>3.0265</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6944</v>
+        <v>1.3472</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6142</v>
+        <v>1.3964</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9198</v>
+        <v>-0.0492</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6982</v>
+        <v>1.2459</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7307</v>
+        <v>1.3211</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0325</v>
+        <v>-0.0752</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0038</v>
+        <v>0.1014</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1165</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8873</v>
+        <v>0.026</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.9677</v>
+        <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>4.3645</v>
+        <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7242</v>
+        <v>0.4875</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2439</v>
+        <v>-0.1246</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4803</v>
+        <v>0.6121</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9613</v>
+        <v>0.9405</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1352</v>
+        <v>1.2065</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1738</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>S. CASAÚ PUEYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3896</v>
+        <v>3.6924</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7236</v>
+        <v>1.3456</v>
       </c>
       <c r="F15" t="n">
-        <v>2.666</v>
+        <v>2.3468</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3472</v>
+        <v>2.5405</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3964</v>
+        <v>1.5325</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0492</v>
+        <v>1.008</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2459</v>
+        <v>2.2164</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3211</v>
+        <v>1.649</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0752</v>
+        <v>0.5674</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1014</v>
+        <v>0.3241</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.1165</v>
       </c>
       <c r="O15" t="n">
-        <v>0.026</v>
+        <v>0.4406</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>2.579</v>
+        <v>2.9758</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4852</v>
+        <v>-0.1261</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7368</v>
+        <v>-0.7481</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2516</v>
+        <v>0.6219</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9405</v>
+        <v>-0.7058</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.266</v>
+        <v>-1.575</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. CASAÚ PUEYO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9722</v>
+        <v>2.8517</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7334000000000001</v>
+        <v>-1.5026</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2388</v>
+        <v>4.3543</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5405</v>
+        <v>0.6944</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5325</v>
+        <v>1.6142</v>
       </c>
       <c r="I16" t="n">
-        <v>1.008</v>
+        <v>-0.9198</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2164</v>
+        <v>1.6982</v>
       </c>
       <c r="K16" t="n">
-        <v>1.649</v>
+        <v>1.7307</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5674</v>
+        <v>-0.0325</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3241</v>
+        <v>-1.0038</v>
       </c>
       <c r="N16" t="n">
         <v>-0.1165</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4406</v>
+        <v>-0.8873</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9758</v>
+        <v>4.3645</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8463000000000001</v>
+        <v>0.7992</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3602</v>
+        <v>-0.3683</v>
       </c>
       <c r="U16" t="n">
-        <v>0.514</v>
+        <v>1.1675</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7058</v>
+        <v>0.9613</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8692</v>
+        <v>1.1352</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.575</v>
+        <v>-0.1738</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9081</v>
+        <v>1.6991</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3716</v>
+        <v>-0.4446</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5365</v>
+        <v>2.1437</v>
       </c>
       <c r="G17" t="n">
         <v>0.3223</v>
@@ -1780,13 +1780,13 @@
         <v>3.3725</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6369</v>
+        <v>0.4279</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6066</v>
+        <v>-0.2096</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0303</v>
+        <v>0.6375</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4398</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3684</v>
+        <v>0.6065</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9113</v>
+        <v>1.0133</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.4068</v>
       </c>
       <c r="G18" t="n">
         <v>0.4295</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3344</v>
+        <v>-0.0964</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3741</v>
+        <v>-0.272</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0396</v>
+        <v>0.1757</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1234</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7477</v>
+        <v>-0.6737</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5098</v>
+        <v>0.6118</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2575</v>
+        <v>-1.2856</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3161</v>
@@ -1936,13 +1936,13 @@
         <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0187</v>
+        <v>0.0553</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1757</v>
+        <v>-0.0737</v>
       </c>
       <c r="U19" t="n">
-        <v>0.157</v>
+        <v>0.1289</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9342</v>
+        <v>-2.5023</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6661</v>
+        <v>-3.4067</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2681</v>
+        <v>0.9045</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5</v>
+        <v>-2.7276</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0633</v>
+        <v>-0.7507</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4368</v>
+        <v>-1.977</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3001</v>
+        <v>-0.2209</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.66</v>
+        <v>-0.226</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.64</v>
+        <v>0.0051</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2</v>
+        <v>-2.5067</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4032</v>
+        <v>-0.5246</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7967</v>
+        <v>-1.9821</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7935</v>
+        <v>3.5709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2358</v>
+        <v>-0.4619</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3741</v>
+        <v>-0.476</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1383</v>
+        <v>0.0141</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.0921</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1738</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0991</v>
+        <v>-2.7863</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6108</v>
+        <v>-2.462</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5117</v>
+        <v>-0.3243</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7276</v>
+        <v>-2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7507</v>
+        <v>-1.0633</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.977</v>
+        <v>-1.4368</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2209</v>
+        <v>-1.3001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.226</v>
+        <v>-0.66</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0051</v>
+        <v>-0.64</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5067</v>
+        <v>-1.2</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5246</v>
+        <v>-0.4032</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9821</v>
+        <v>-0.7967</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>3.5709</v>
+        <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0587</v>
+        <v>-0.0878</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.68</v>
+        <v>-0.17</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3787</v>
+        <v>0.0822</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0921</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2239</v>
+        <v>-5.4511</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3246</v>
+        <v>-4.9165</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8993</v>
+        <v>-0.5346</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7394</v>
@@ -2170,13 +2170,13 @@
         <v>2.3806</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6443</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2469</v>
+        <v>-0.8388</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3974</v>
+        <v>-0.0327</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2451</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.8752</v>
+        <v>6.555399999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.529300000000001</v>
+        <v>-5.529299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>11.4047</v>
+        <v>12.0847</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6641999999999992</v>
@@ -2218,7 +2218,7 @@
         <v>3.9346</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.598800000000001</v>
+        <v>-4.5988</v>
       </c>
       <c r="J23" t="n">
         <v>7.3789</v>
@@ -2227,7 +2227,7 @@
         <v>7.541399999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1623999999999999</v>
+        <v>-0.1624000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-8.043100000000001</v>
@@ -2236,10 +2236,10 @@
         <v>-3.6066</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.436299999999999</v>
+        <v>-4.4363</v>
       </c>
       <c r="P23" t="n">
-        <v>6.9435</v>
+        <v>6.943499999999998</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.8788</v>
@@ -2248,16 +2248,16 @@
         <v>21.8223</v>
       </c>
       <c r="S23" t="n">
-        <v>0.05669999999999953</v>
+        <v>0.7369</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.1733</v>
+        <v>-3.1734</v>
       </c>
       <c r="U23" t="n">
-        <v>3.23</v>
+        <v>3.9102</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4606999999999997</v>
+        <v>-0.4606999999999998</v>
       </c>
       <c r="W23" t="n">
         <v>5.1441</v>
